--- a/TeacherTraining/templates/master-holidays-template.xlsx
+++ b/TeacherTraining/templates/master-holidays-template.xlsx
@@ -45,7 +45,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
